--- a/models/Technogym_DCF_Model.xlsx
+++ b/models/Technogym_DCF_Model.xlsx
@@ -37,7 +37,7 @@
     <numFmt numFmtId="167" formatCode="0.0x"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,6 +103,16 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000000FF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -153,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,6 +220,9 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6555,7 +6568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7036,6 +7049,131 @@
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Cash conversion (recurring pre-tax FCF / EBITDA): 86% (2024) → 82% (2025). ROCE ≈ 24% (2025, approx).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>H1-2026 INTERIM CHECKPOINT (unaudited, vs H1-2025) — added 03-Sep-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="56" t="inlineStr">
+        <is>
+          <t>H1 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="56" t="inlineStr">
+        <is>
+          <t>H1 2025</t>
+        </is>
+      </c>
+      <c r="D41" s="56" t="inlineStr">
+        <is>
+          <t>% chg / delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B42" s="57" t="n">
+        <v>492.6</v>
+      </c>
+      <c r="C42" s="57" t="n">
+        <v>458.8</v>
+      </c>
+      <c r="D42">
+        <f>B42/C42-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Americas revenue</t>
+        </is>
+      </c>
+      <c r="B43" s="57" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="C43" s="57" t="n">
+        <v>77</v>
+      </c>
+      <c r="D43">
+        <f>B43/C43-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Adj. EBITDA</t>
+        </is>
+      </c>
+      <c r="B44" s="57" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="C44" s="57" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D44">
+        <f>B44/C44-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Adj. EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B45" s="57">
+        <f>B44/B42</f>
+        <v/>
+      </c>
+      <c r="C45" s="57">
+        <f>C44/C42</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>B45-C45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Recurring FCF (pre-tax)</t>
+        </is>
+      </c>
+      <c r="B46" s="57" t="n">
+        <v>20</v>
+      </c>
+      <c r="C46" s="57" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="D46">
+        <f>B46/C46-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="58" t="inlineStr">
+        <is>
+          <t>Digital/MyWellness KPI disclosure: none (unchanged).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="58" t="inlineStr">
+        <is>
+          <t>Source: Technogym H1-2026 board press release, 30 Jul 2026 (corporate.technogym.com investor relations). Confirms memo thesis test: Americas did not stabilize (-1.1%), margin broke -- first reversal since the 2021-2025 uptrend shown in row 26 -- and no digital disclosure. HOLD rating and EUR15.72 base fair value unchanged; see 00 Executive Summary.</t>
         </is>
       </c>
     </row>
